--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_PSC.xlsx
@@ -422,23 +422,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>PSC_G._ROSADO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>G. Rosado</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PSC_H._SOTTA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H. Sotta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PSC_T._COLEMAN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>23.3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PSC_P._BASTOS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -453,24 +824,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>G. Rosado | M. Landdeck</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E2" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-30.2</v>
       </c>
     </row>
   </sheetData>
@@ -484,12 +913,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,32 +975,66 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>G. Rosado</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>G. Rosado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
@@ -632,16 +1095,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
@@ -651,16 +1114,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100.5</v>
+        <v>93.7</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>-9.9</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +1133,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>110.8</v>
+        <v>118.8</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="5">
@@ -689,16 +1152,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-10.3</v>
+        <v>-25.1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.3</v>
+        <v>-24.7</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +1171,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
@@ -733,7 +1196,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -749,7 +1212,7 @@
         <v>0.3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -765,16 +1228,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>20.5</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="10">
@@ -790,10 +1253,10 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +1272,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -865,7 +1328,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ball movement is close to league average; they can share it but are not purely pass-first.</t>
+          <t>Above-average assist profile; expect cleaner passing sequences and more extra-pass possessions.</t>
         </is>
       </c>
     </row>
@@ -877,7 +1340,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
         </is>
       </c>
     </row>
@@ -901,7 +1364,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Above-average foul volume; contact pressure and discipline both matter in this matchup.</t>
+          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -967,7 +1430,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Win the first action: they do not consistently hurt teams with second-chance volume, so clean first stops carry value.</t>
+          <t>Know the first reference: G. Rosado is a paint finisher, and the plan should start with taking away his comfort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Closeout discipline matters: P. Bastos, M. Landdeck are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -982,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1004,48 +1479,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from M. Landdeck and L. Rahama; contest, but do not over-help into secondary advantages.</t>
+          <t>The main offensive references are G. Rosado and M. Landdeck; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Paint Non-RA; protect that area early in possessions.</t>
+          <t>Priority closeouts start with P. Bastos and M. Landdeck; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially T. Coleman, M. Landdeck, and G. Rosado; force them away from preferred areas.</t>
+          <t>Some perimeter volume comes from M. Landdeck and P. Oliveira; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Several players have clear comfort zones, especially G. Rosado, M. Landdeck, and T. Coleman; force them away from preferred areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Recognize the main duo/trio combinations: G. Rosado | M. Landdeck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Do not lose P. Bastos and M. Landdeck in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1060,23 +1583,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>PSC_G._ROSADO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>G. Rosado</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>bench spacer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PSC_H._SOTTA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H. Sotta</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PSC_T._COLEMAN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>inside scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PSC_P._BASTOS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1185,37 +1959,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1231,41 +2005,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1282,36 +2056,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1328,16 +2102,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PSC_H._SOTTA</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>H. Sotta</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1346,14 +2120,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1369,74 +2143,94 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>25</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>37.3%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PSC_H._SOTTA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>H. Sotta</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>20</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>29.9%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1454,23 +2248,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
     </row>
@@ -1490,23 +2284,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
     </row>
@@ -1526,42 +2320,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PSC_T._COLEMAN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>T. Coleman</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -1570,42 +2356,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PSC_M._LANDDECK</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>M. Landdeck</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -1614,23 +2392,23 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -1658,23 +2436,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -1686,12 +2464,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1702,23 +2480,243 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PSC_T._COLEMAN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
+        <v>9</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>6</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="M16" t="n">
         <v>0.3</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PSC_P._BASTOS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PSC_J._GREWAL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>J. Grewal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>29.4%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_PSC.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,36 +515,36 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -567,36 +567,36 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -608,84 +608,84 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSC_H._SOTTA</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H. Sotta</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -695,119 +695,275 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_H._SOTTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>H. Sotta</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PSC_P._BASTOS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PSC_P._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P. Oliveira</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -824,12 +980,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -890,16 +1046,103 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>77.3</v>
       </c>
       <c r="E2" t="n">
-        <v>71.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>102.1</v>
+        <v>96.7</v>
       </c>
       <c r="G2" t="n">
-        <v>-30.2</v>
+        <v>-19.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>D. Fragoso | G. Rosado</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>D. Fragoso | G. Rosado</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>G. Rosado | M. Landdeck | T. Coleman</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-22.8</v>
       </c>
     </row>
   </sheetData>
@@ -913,12 +1156,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1009,32 +1252,66 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>lineups</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>base_lineup</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman (15.3 min)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman (-23.5 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
@@ -1095,16 +1372,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -1114,16 +1391,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>-12.6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="4">
@@ -1133,16 +1410,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>118.8</v>
+        <v>116.3</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>12.1</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="5">
@@ -1152,16 +1429,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-25.1</v>
+        <v>-19.7</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>-24.7</v>
+        <v>-19.4</v>
       </c>
     </row>
     <row r="6">
@@ -1171,16 +1448,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>21.3</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1196,7 +1473,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1215,7 +1492,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>-0</v>
@@ -1228,16 +1505,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1253,7 +1530,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0.1</v>
@@ -1272,7 +1549,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -1340,7 +1617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1430,7 +1707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Know the first reference: G. Rosado is a paint finisher, and the plan should start with taking away his comfort.</t>
+          <t>Win the first action: they do not consistently hurt teams with second-chance volume, so clean first stops carry value.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1719,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Closeout discipline matters: P. Bastos, M. Landdeck are the first perimeter names you cannot lose in help situations.</t>
+          <t>Know the first reference: G. Rosado is a paint finisher, and the plan should start with taking away his comfort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Closeout discipline matters: P. Bastos, J. Grewal are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with P. Bastos and M. Landdeck; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with P. Bastos, J. Grewal, and M. Landdeck; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from M. Landdeck and P. Oliveira; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from M. Landdeck and J. Grewal; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1809,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
+          <t>Their offense naturally flows toward Paint Non-RA; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1821,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially G. Rosado, M. Landdeck, and T. Coleman; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially M. Landdeck, T. Coleman, and G. Rosado; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1833,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: G. Rosado | M. Landdeck.</t>
+          <t>Recognize the main duo/trio combinations: G. Rosado | M. Landdeck and D. Fragoso | G. Rosado.</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1845,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1857,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Do not lose P. Bastos and M. Landdeck in help-and-recover situations.</t>
+          <t>Do not lose P. Bastos and J. Grewal in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1882,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1650,10 +1939,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31.6</v>
+        <v>32.8</v>
       </c>
       <c r="D2" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -1686,17 +1975,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.4</v>
+        <v>30.4</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1706,141 +1995,141 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>bench spacer</t>
+          <t>primary handler</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26.7</v>
+        <v>25.4</v>
       </c>
       <c r="D4" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>inside scorer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSC_H._SOTTA</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H. Sotta</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24.5</v>
+        <v>23.4</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_H._SOTTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>H. Sotta</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.3</v>
+        <v>21.4</v>
       </c>
       <c r="D6" t="n">
-        <v>9.5</v>
+        <v>2.3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>inside scorer</t>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.8</v>
+        <v>20.1</v>
       </c>
       <c r="D7" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1865,7 +2154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1973,20 +2262,20 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -2010,32 +2299,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2051,7 +2340,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2065,23 +2354,23 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2102,32 +2391,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PSC_P._OLIVEIRA</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P. Oliveira</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2148,32 +2437,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PSC_H._SOTTA</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>H. Sotta</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2194,36 +2483,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_H._SOTTA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>H. Sotta</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -2235,38 +2524,48 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>38</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>31.6%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>28.8%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2284,23 +2583,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>30.9%</t>
         </is>
       </c>
     </row>
@@ -2320,23 +2619,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>28.2%</t>
         </is>
       </c>
     </row>
@@ -2356,23 +2655,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
@@ -2392,42 +2691,34 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PSC_G._ROSADO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>G. Rosado</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2436,23 +2727,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>8.0%</t>
         </is>
       </c>
     </row>
@@ -2484,19 +2775,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -2528,11 +2819,11 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -2552,12 +2843,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2568,23 +2859,23 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2887,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2612,23 +2903,23 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2931,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2660,19 +2951,19 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2975,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2704,19 +2995,107 @@
         </is>
       </c>
       <c r="K19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PSC_P._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P. Oliveira</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>5</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>29.4%</t>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>41.7%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_PSC.xlsx
@@ -515,36 +515,36 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -567,36 +567,36 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -619,41 +619,41 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -671,31 +671,31 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -723,41 +723,41 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -775,88 +775,88 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -868,12 +868,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -883,32 +883,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -920,47 +920,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PSC_P._OLIVEIRA</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P. Oliveira</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>77.3</v>
+        <v>108.1</v>
       </c>
       <c r="E2" t="n">
-        <v>77.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="F2" t="n">
-        <v>96.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-19.7</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="3">
@@ -1075,16 +1075,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>57.1</v>
+        <v>79</v>
       </c>
       <c r="E3" t="n">
-        <v>74.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>83.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>-9.1</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="4">
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>57.1</v>
+        <v>79</v>
       </c>
       <c r="E4" t="n">
-        <v>74.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>83.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
-        <v>-9.1</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="5">
@@ -1133,16 +1133,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>49.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>69.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>91.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-22.8</v>
+        <v>-13.5</v>
       </c>
     </row>
   </sheetData>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman (15.3 min)</t>
+          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman (16.2 min)</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman (-23.5 net)</t>
+          <t>D. Fragoso | G. Rosado | M. Landdeck | P. Oliveira | T. Coleman (20.0 net)</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
     </row>
@@ -1372,16 +1372,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.3</v>
+        <v>80.5</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3">
@@ -1391,16 +1391,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>-9</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116.3</v>
+        <v>111</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>10.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-19.7</v>
+        <v>-15.4</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>-19.4</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="6">
@@ -1448,16 +1448,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.3</v>
+        <v>19.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
         <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1476,7 +1476,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -1492,7 +1492,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>-0</v>
@@ -1505,16 +1505,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10">
@@ -1530,7 +1530,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0.1</v>
@@ -1549,7 +1549,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
+          <t>Above-average foul volume; contact pressure and discipline both matter in this matchup.</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Know the first reference: G. Rosado is a paint finisher, and the plan should start with taking away his comfort.</t>
+          <t>Know the first reference: G. Rosado is a inside scorer, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Paint Non-RA; protect that area early in possessions.</t>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
@@ -1939,27 +1939,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32.8</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>inside scorer</t>
         </is>
       </c>
     </row>
@@ -1975,17 +1975,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.4</v>
+        <v>31.1</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>15.2</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="D4" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2083,17 +2083,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.4</v>
+        <v>20.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2119,17 +2119,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.1</v>
+        <v>18.6</v>
       </c>
       <c r="D7" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -2308,20 +2308,20 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
         <v>0.8</v>
@@ -2354,20 +2354,20 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="H4" t="n">
         <v>0.8</v>
@@ -2400,20 +2400,20 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="H5" t="n">
         <v>0.8</v>
@@ -2446,20 +2446,20 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H6" t="n">
         <v>0.8</v>
@@ -2492,23 +2492,23 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2529,36 +2529,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -2583,15 +2583,15 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>28.5%</t>
         </is>
       </c>
     </row>
@@ -2619,23 +2619,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -2659,19 +2659,19 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
     </row>
@@ -2695,19 +2695,19 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -2731,11 +2731,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -2775,19 +2775,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -2819,19 +2819,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>48.6%</t>
         </is>
       </c>
     </row>
@@ -2859,23 +2859,23 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
     </row>
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
     </row>
@@ -2975,12 +2975,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2991,23 +2991,23 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -3019,12 +3019,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -3035,7 +3035,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -3043,15 +3043,15 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -3083,19 +3083,19 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>40.0%</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>41.7%</t>
         </is>
       </c>
     </row>
